--- a/artfynd/A 5627-2025 artfynd.xlsx
+++ b/artfynd/A 5627-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132406943</v>
+        <v>132406948</v>
       </c>
       <c r="B2" t="n">
-        <v>57957</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532656</v>
+        <v>532600</v>
       </c>
       <c r="R2" t="n">
-        <v>7114430</v>
+        <v>7114489</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +755,13 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -808,7 +803,7 @@
         <v>132406949</v>
       </c>
       <c r="B3" t="n">
-        <v>92215</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406937</v>
+        <v>132406950</v>
       </c>
       <c r="B4" t="n">
-        <v>91916</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +936,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532370</v>
+        <v>532565</v>
       </c>
       <c r="R4" t="n">
-        <v>7114372</v>
+        <v>7114437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1055,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406955</v>
+        <v>132406951</v>
       </c>
       <c r="B5" t="n">
-        <v>79332</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,26 +1061,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532350</v>
+        <v>532466</v>
       </c>
       <c r="R5" t="n">
-        <v>7114399</v>
+        <v>7114428</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,21 +1143,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1176,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406951</v>
+        <v>132406931</v>
       </c>
       <c r="B6" t="n">
-        <v>91912</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,21 +1171,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1218,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532466</v>
+        <v>532599</v>
       </c>
       <c r="R6" t="n">
-        <v>7114428</v>
+        <v>7114492</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1269,6 +1253,21 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1286,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406939</v>
+        <v>132406933</v>
       </c>
       <c r="B7" t="n">
-        <v>57957</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,29 +1296,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1329,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532658</v>
+        <v>532588</v>
       </c>
       <c r="R7" t="n">
-        <v>7114442</v>
+        <v>7114486</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,17 +1365,13 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1416,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406942</v>
+        <v>132406934</v>
       </c>
       <c r="B8" t="n">
-        <v>57957</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,29 +1421,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1459,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532446</v>
+        <v>532530</v>
       </c>
       <c r="R8" t="n">
-        <v>7114442</v>
+        <v>7114406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1497,17 +1490,13 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1546,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132406953</v>
+        <v>132406935</v>
       </c>
       <c r="B9" t="n">
-        <v>79332</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,26 +1546,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1584,10 +1577,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532559</v>
+        <v>532400</v>
       </c>
       <c r="R9" t="n">
-        <v>7114473</v>
+        <v>7114391</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1667,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132406931</v>
+        <v>132406936</v>
       </c>
       <c r="B10" t="n">
-        <v>91916</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,10 +1702,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532599</v>
+        <v>532365</v>
       </c>
       <c r="R10" t="n">
-        <v>7114492</v>
+        <v>7114358</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1792,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406952</v>
+        <v>132406937</v>
       </c>
       <c r="B11" t="n">
-        <v>91930</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,21 +1796,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1834,10 +1827,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532453</v>
+        <v>532370</v>
       </c>
       <c r="R11" t="n">
-        <v>7114410</v>
+        <v>7114372</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1885,6 +1878,21 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1902,10 +1910,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406948</v>
+        <v>132406938</v>
       </c>
       <c r="B12" t="n">
-        <v>92215</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,21 +1921,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1944,10 +1952,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532600</v>
+        <v>532367</v>
       </c>
       <c r="R12" t="n">
-        <v>7114489</v>
+        <v>7114380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2027,37 +2035,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406946</v>
+        <v>132406952</v>
       </c>
       <c r="B13" t="n">
-        <v>80341</v>
+        <v>91988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2065,10 +2077,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532350</v>
+        <v>532453</v>
       </c>
       <c r="R13" t="n">
-        <v>7114405</v>
+        <v>7114410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2116,21 +2128,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2148,10 +2145,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406935</v>
+        <v>132406947</v>
       </c>
       <c r="B14" t="n">
-        <v>91916</v>
+        <v>92406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,21 +2156,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2190,10 +2187,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532400</v>
+        <v>532414</v>
       </c>
       <c r="R14" t="n">
-        <v>7114391</v>
+        <v>7114418</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2273,41 +2270,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132406950</v>
+        <v>132406953</v>
       </c>
       <c r="B15" t="n">
-        <v>91912</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2315,10 +2308,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532565</v>
+        <v>532559</v>
       </c>
       <c r="R15" t="n">
-        <v>7114437</v>
+        <v>7114473</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2398,41 +2391,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132406934</v>
+        <v>132406954</v>
       </c>
       <c r="B16" t="n">
-        <v>91916</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2440,10 +2429,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532530</v>
+        <v>532363</v>
       </c>
       <c r="R16" t="n">
-        <v>7114406</v>
+        <v>7114343</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2523,41 +2512,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132406936</v>
+        <v>132406955</v>
       </c>
       <c r="B17" t="n">
-        <v>91916</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2565,10 +2550,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532365</v>
+        <v>532350</v>
       </c>
       <c r="R17" t="n">
-        <v>7114358</v>
+        <v>7114399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2648,10 +2633,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132406940</v>
+        <v>132406930</v>
       </c>
       <c r="B18" t="n">
-        <v>57957</v>
+        <v>83358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,31 +2644,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2691,10 +2671,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532550</v>
+        <v>532357</v>
       </c>
       <c r="R18" t="n">
-        <v>7114391</v>
+        <v>7114401</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2729,17 +2709,13 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2778,41 +2754,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132406947</v>
+        <v>132406946</v>
       </c>
       <c r="B19" t="n">
-        <v>92376</v>
+        <v>80382</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2820,10 +2792,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532414</v>
+        <v>532350</v>
       </c>
       <c r="R19" t="n">
-        <v>7114418</v>
+        <v>7114405</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2875,17 +2847,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2903,10 +2875,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132406930</v>
+        <v>132406939</v>
       </c>
       <c r="B20" t="n">
-        <v>83314</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2914,26 +2886,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2941,10 +2918,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532357</v>
+        <v>532658</v>
       </c>
       <c r="R20" t="n">
-        <v>7114401</v>
+        <v>7114442</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2979,13 +2956,17 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3024,10 +3005,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132406938</v>
+        <v>132406940</v>
       </c>
       <c r="B21" t="n">
-        <v>91916</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,28 +3016,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3066,10 +3048,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532367</v>
+        <v>532550</v>
       </c>
       <c r="R21" t="n">
-        <v>7114380</v>
+        <v>7114391</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3104,13 +3086,17 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3149,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132406933</v>
+        <v>132406941</v>
       </c>
       <c r="B22" t="n">
-        <v>91916</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,28 +3146,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3191,10 +3178,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532588</v>
+        <v>532565</v>
       </c>
       <c r="R22" t="n">
-        <v>7114486</v>
+        <v>7114395</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3229,13 +3216,17 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3274,10 +3265,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132406944</v>
+        <v>132406942</v>
       </c>
       <c r="B23" t="n">
-        <v>58118</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3285,50 +3276,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hägnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532462</v>
+        <v>532446</v>
       </c>
       <c r="R23" t="n">
-        <v>7114376</v>
+        <v>7114442</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3363,6 +3346,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3377,9 +3365,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med flerskiktning och murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3397,10 +3395,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132406954</v>
+        <v>132406943</v>
       </c>
       <c r="B24" t="n">
-        <v>79332</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3408,26 +3406,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3435,10 +3438,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532363</v>
+        <v>532656</v>
       </c>
       <c r="R24" t="n">
-        <v>7114343</v>
+        <v>7114430</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3473,13 +3476,17 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3518,10 +3525,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132406941</v>
+        <v>132406944</v>
       </c>
       <c r="B25" t="n">
-        <v>57957</v>
+        <v>58136</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3529,42 +3536,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hägnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532565</v>
+        <v>532462</v>
       </c>
       <c r="R25" t="n">
-        <v>7114395</v>
+        <v>7114376</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3599,11 +3614,6 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran. Skogsbeståndet för fyndplatsen hyser stående död ved som indikerar höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3618,19 +3628,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med flerskiktning och murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 5627-2025 artfynd.xlsx
+++ b/artfynd/A 5627-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406948</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406949</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406950</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406951</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406931</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1407,6 +1437,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406933</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1532,6 +1567,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406934</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1657,6 +1697,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406935</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1782,6 +1827,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406936</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1907,6 +1957,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406937</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2032,6 +2087,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406938</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2142,6 +2202,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406952</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2267,6 +2332,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406947</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2388,6 +2458,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406953</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2509,6 +2584,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406954</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2630,6 +2710,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406955</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2751,6 +2836,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406930</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2872,6 +2962,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406946</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3002,6 +3097,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406939</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3132,6 +3232,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406940</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3262,6 +3367,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406941</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3392,6 +3502,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406942</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3522,6 +3637,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406943</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3645,8 +3765,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406944</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>